--- a/ALL/A3-Pinterest_03-out/Recipes.xlsx
+++ b/ALL/A3-Pinterest_03-out/Recipes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,14 +439,38 @@
           <t>Recipe</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Generated At</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Json Recipe</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Prompt</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Prompt Image Ingredients</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pizza</t>
+          <t>Spicy Honey Glazed Salmon</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
